--- a/templates/Шаблоны МП.xlsx
+++ b/templates/Шаблоны МП.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\media_planner\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2D91CC-BF6C-4384-B246-8F7665CBD7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1803D0EE-A8BA-4A58-8727-D6DBF7FB7E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="МП_Total" sheetId="3" r:id="rId1"/>
@@ -1223,7 +1223,7 @@
         <v>-</v>
       </c>
       <c r="AB4" s="15">
-        <f>IFERROR(МП_Periods!O4+МП_Periods!O17+МП_Periods!O30+МП_Periods!O48+МП_Periods!O56+МП_Periods!O69+МП_Periods!O82+МП_Periods!O95+МП_Periods!O108+МП_Periods!O121+МП_Periods!O134+МП_Periods!O147,"-")</f>
+        <f>SUM(МП_Periods!O4,МП_Periods!O17,МП_Periods!O30,МП_Periods!O43,МП_Periods!O56,МП_Periods!O69,МП_Periods!O82,МП_Periods!O95,МП_Periods!O108,МП_Periods!O121,МП_Periods!O134,МП_Periods!O147)</f>
         <v>0</v>
       </c>
       <c r="AC4" s="15">
@@ -1387,7 +1387,7 @@
         <v>-</v>
       </c>
       <c r="AB5" s="15">
-        <f>IFERROR(МП_Periods!O5+МП_Periods!O18+МП_Periods!O31+МП_Periods!O44+МП_Periods!O57+МП_Periods!O70+МП_Periods!O83+МП_Periods!O96+МП_Periods!O109+МП_Periods!O122+МП_Periods!O135+МП_Periods!O148,"-")</f>
+        <f>SUM(МП_Periods!O5,МП_Periods!O18,МП_Periods!O31,МП_Periods!O44,МП_Periods!O57,МП_Periods!O70,МП_Periods!O83,МП_Periods!O96,МП_Periods!O109,МП_Periods!O122,МП_Periods!O135,МП_Periods!O148)</f>
         <v>0</v>
       </c>
       <c r="AC5" s="15">
@@ -1551,7 +1551,7 @@
         <v>-</v>
       </c>
       <c r="AB6" s="15">
-        <f>IFERROR(МП_Periods!O6+МП_Periods!O19+МП_Periods!O32+МП_Periods!O45+МП_Periods!O58+МП_Periods!O71+МП_Periods!O84+МП_Periods!O97+МП_Periods!O110+МП_Periods!O123+МП_Periods!O136+МП_Periods!O149,"-")</f>
+        <f>SUM(МП_Periods!O6,МП_Periods!O19,МП_Periods!O32,МП_Periods!O45,МП_Periods!O58,МП_Periods!O71,МП_Periods!O84,МП_Periods!O97,МП_Periods!O110,МП_Periods!O123,МП_Periods!O136,МП_Periods!O149)</f>
         <v>0</v>
       </c>
       <c r="AC6" s="15">
@@ -1715,7 +1715,7 @@
         <v>-</v>
       </c>
       <c r="AB7" s="15">
-        <f>IFERROR(МП_Periods!O7+МП_Periods!O20+МП_Periods!O33+МП_Periods!O46+МП_Periods!O59+МП_Periods!O72+МП_Periods!O85+МП_Periods!O98+МП_Periods!O111+МП_Periods!O124+МП_Periods!O137+МП_Periods!O150,"-")</f>
+        <f>SUM(МП_Periods!O7,МП_Periods!O20,МП_Periods!O33,МП_Periods!O46,МП_Periods!O59,МП_Periods!O72,МП_Periods!O85,МП_Periods!O98,МП_Periods!O111,МП_Periods!O124,МП_Periods!O137,МП_Periods!O150)</f>
         <v>0</v>
       </c>
       <c r="AC7" s="15">
@@ -1879,7 +1879,7 @@
         <v>-</v>
       </c>
       <c r="AB8" s="15">
-        <f>IFERROR(МП_Periods!O8+МП_Periods!O21+МП_Periods!O34+МП_Periods!O47+МП_Periods!O60+МП_Periods!O73+МП_Periods!O86+МП_Periods!O99+МП_Periods!O112+МП_Periods!O125+МП_Periods!O138+МП_Periods!O151,"-")</f>
+        <f>SUM(МП_Periods!O8,МП_Periods!O21,МП_Periods!O34,МП_Periods!O47,МП_Periods!O60,МП_Periods!O73,МП_Periods!O86,МП_Periods!O99,МП_Periods!O112,МП_Periods!O125,МП_Periods!O138,МП_Periods!O151)</f>
         <v>0</v>
       </c>
       <c r="AC8" s="15">
@@ -2043,7 +2043,7 @@
         <v>-</v>
       </c>
       <c r="AB9" s="15">
-        <f>IFERROR(МП_Periods!O9+МП_Periods!O22+МП_Periods!O35+МП_Periods!O48+МП_Periods!O61+МП_Periods!O74+МП_Periods!O87+МП_Periods!O100+МП_Periods!O113+МП_Periods!O126+МП_Periods!O139+МП_Periods!O152,"-")</f>
+        <f>SUM(МП_Periods!O9,МП_Periods!O22,МП_Periods!O35,МП_Periods!O48,МП_Periods!O61,МП_Periods!O74,МП_Periods!O87,МП_Periods!O100,МП_Periods!O113,МП_Periods!O126,МП_Periods!O139,МП_Periods!O152)</f>
         <v>0</v>
       </c>
       <c r="AC9" s="15">
@@ -2207,7 +2207,7 @@
         <v>-</v>
       </c>
       <c r="AB10" s="15">
-        <f>IFERROR(МП_Periods!O10+МП_Periods!O23+МП_Periods!O36+МП_Periods!O49+МП_Periods!O62+МП_Periods!O75+МП_Periods!O88+МП_Periods!O101+МП_Periods!O114+МП_Periods!O127+МП_Periods!O140+МП_Periods!O153,"-")</f>
+        <f>SUM(МП_Periods!O10,МП_Periods!O23,МП_Periods!O36,МП_Periods!O49,МП_Periods!O62,МП_Periods!O75,МП_Periods!O88,МП_Periods!O101,МП_Periods!O114,МП_Periods!O127,МП_Periods!O140,МП_Periods!O153)</f>
         <v>0</v>
       </c>
       <c r="AC10" s="15">
@@ -2371,7 +2371,7 @@
         <v>-</v>
       </c>
       <c r="AB11" s="15">
-        <f>IFERROR(МП_Periods!O11+МП_Periods!O24+МП_Periods!O37+МП_Periods!O50+МП_Periods!O63+МП_Periods!O76+МП_Periods!O89+МП_Periods!O102+МП_Periods!O115+МП_Periods!O128+МП_Periods!O141+МП_Periods!O154,"-")</f>
+        <f>SUM(МП_Periods!O11,МП_Periods!O24,МП_Periods!O37,МП_Periods!O50,МП_Periods!O63,МП_Periods!O76,МП_Periods!O89,МП_Periods!O102,МП_Periods!O115,МП_Periods!O128,МП_Periods!O141,МП_Periods!O154)</f>
         <v>0</v>
       </c>
       <c r="AC11" s="15">
@@ -2535,7 +2535,7 @@
         <v>-</v>
       </c>
       <c r="AB12" s="15">
-        <f>IFERROR(МП_Periods!O12+МП_Periods!O25+МП_Periods!O38+МП_Periods!O51+МП_Periods!O64+МП_Periods!O77+МП_Periods!O90+МП_Periods!O103+МП_Periods!O116+МП_Periods!O129+МП_Periods!O142+МП_Periods!O155,"-")</f>
+        <f>SUM(МП_Periods!O12,МП_Periods!O25,МП_Periods!O38,МП_Periods!O51,МП_Periods!O64,МП_Periods!O77,МП_Periods!O90,МП_Periods!O103,МП_Periods!O116,МП_Periods!O129,МП_Periods!O142,МП_Periods!O155)</f>
         <v>0</v>
       </c>
       <c r="AC12" s="15">
